--- a/public/docs/Matrix.xlsx
+++ b/public/docs/Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\kayaba-training-centre\public\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C29D6AA-E662-4F63-AB55-4133E615DACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B3D5F4-4766-4BB9-83F4-662D514D599D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A0F0ECB8-F82F-4053-9817-EFE29D066A77}"/>
   </bookViews>
